--- a/artfynd/A 17082-2022 artfynd.xlsx
+++ b/artfynd/A 17082-2022 artfynd.xlsx
@@ -889,7 +889,7 @@
         <v>136489980</v>
       </c>
       <c r="B4" t="n">
-        <v>93392</v>
+        <v>93395</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>136044762</v>
       </c>
       <c r="B6" t="n">
-        <v>93044</v>
+        <v>93047</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 17082-2022 artfynd.xlsx
+++ b/artfynd/A 17082-2022 artfynd.xlsx
@@ -889,7 +889,7 @@
         <v>136489980</v>
       </c>
       <c r="B4" t="n">
-        <v>93395</v>
+        <v>93396</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>136044762</v>
       </c>
       <c r="B6" t="n">
-        <v>93047</v>
+        <v>93048</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 17082-2022 artfynd.xlsx
+++ b/artfynd/A 17082-2022 artfynd.xlsx
@@ -889,7 +889,7 @@
         <v>136489980</v>
       </c>
       <c r="B4" t="n">
-        <v>93396</v>
+        <v>93401</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 17082-2022 artfynd.xlsx
+++ b/artfynd/A 17082-2022 artfynd.xlsx
@@ -889,7 +889,7 @@
         <v>136489980</v>
       </c>
       <c r="B4" t="n">
-        <v>93401</v>
+        <v>93403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 17082-2022 artfynd.xlsx
+++ b/artfynd/A 17082-2022 artfynd.xlsx
@@ -889,7 +889,7 @@
         <v>136489980</v>
       </c>
       <c r="B4" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 17082-2022 artfynd.xlsx
+++ b/artfynd/A 17082-2022 artfynd.xlsx
@@ -889,7 +889,7 @@
         <v>136489980</v>
       </c>
       <c r="B4" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 17082-2022 artfynd.xlsx
+++ b/artfynd/A 17082-2022 artfynd.xlsx
@@ -889,7 +889,7 @@
         <v>136489980</v>
       </c>
       <c r="B4" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 17082-2022 artfynd.xlsx
+++ b/artfynd/A 17082-2022 artfynd.xlsx
@@ -889,7 +889,7 @@
         <v>136489980</v>
       </c>
       <c r="B4" t="n">
-        <v>93408</v>
+        <v>93414</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 17082-2022 artfynd.xlsx
+++ b/artfynd/A 17082-2022 artfynd.xlsx
@@ -889,7 +889,7 @@
         <v>136489980</v>
       </c>
       <c r="B4" t="n">
-        <v>93414</v>
+        <v>93418</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
